--- a/KONSPEKT UTWORÓW - NPR.xlsx
+++ b/KONSPEKT UTWORÓW - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A29234-E744-4021-869D-E0E8F7B617B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C51436D-9263-43B3-9914-DAEC5D676A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="339">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -1032,6 +1032,24 @@
   </si>
   <si>
     <t xml:space="preserve">Szybki riff, zbudowany w oparciu o melodyczne ogrywanie skali. Uwaga, musisz posiadać efekt vibrato. </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Qzvr7v1kqcg&amp;t=7s</t>
+  </si>
+  <si>
+    <t>https://youtu.be/nofN1kjTRO8?si=blcZ5kA-VOJe9cjt</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UqUZq1ildfo?si=BAAC_dlVoRa-4k2n</t>
+  </si>
+  <si>
+    <t>https://youtu.be/oBhE2utVI5s?si=X3948eO6H1zYqpJM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kq00CWzhfT0?si=YLylXbnSfMCtdARy</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jw8xYejrIUY?si=apLg-EEwbRPU29im</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1140,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1135,6 +1153,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1684,7 +1703,7 @@
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="68.140625" customWidth="1"/>
     <col min="7" max="7" width="29.85546875" customWidth="1"/>
@@ -1827,8 +1846,8 @@
       <c r="B7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>46</v>
+      <c r="C7" s="10" t="s">
+        <v>337</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>197</v>
@@ -2059,8 +2078,8 @@
       <c r="B19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>46</v>
+      <c r="C19" s="10" t="s">
+        <v>338</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>209</v>
@@ -3393,8 +3412,8 @@
       <c r="B89" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>46</v>
+      <c r="C89" s="10" t="s">
+        <v>334</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>279</v>
@@ -3526,8 +3545,8 @@
       <c r="B96" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>44</v>
+      <c r="C96" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>286</v>
@@ -3735,8 +3754,8 @@
       <c r="B107" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C107" s="5" t="s">
-        <v>46</v>
+      <c r="C107" s="10" t="s">
+        <v>336</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>297</v>
@@ -3925,8 +3944,8 @@
       <c r="B117" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C117" s="5" t="s">
-        <v>46</v>
+      <c r="C117" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>307</v>
@@ -4129,9 +4148,17 @@
       <c r="G128" s="8"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C117" r:id="rId1" xr:uid="{E336D330-01D4-458D-BDE6-2A361C74F038}"/>
+    <hyperlink ref="C89" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
+    <hyperlink ref="C96" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
+    <hyperlink ref="C107" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{BBF384E5-8C25-4A18-BE7D-85EEC8392C4E}"/>
+    <hyperlink ref="C19" r:id="rId6" xr:uid="{91A4A065-747A-407A-B0CE-5F9B3BF29972}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT UTWORÓW - NPR.xlsx
+++ b/KONSPEKT UTWORÓW - NPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C51436D-9263-43B3-9914-DAEC5D676A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C37E47D-8618-4466-A9B9-B8D1AED4B1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="364">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -182,9 +182,6 @@
     <t>Łzy</t>
   </si>
   <si>
-    <t>Ale Wkoło Jest Wesoło</t>
-  </si>
-  <si>
     <t>Perfect</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
     <t>White 2115</t>
   </si>
   <si>
-    <t>Cała w Trawie</t>
-  </si>
-  <si>
     <t>Dżem</t>
   </si>
   <si>
@@ -626,9 +620,6 @@
     <t>https://drive.google.com/open?id=1UWSLDPXtwHeJHzH7NzZLVqsYHGNZk-03&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1UXkdXEpthaSINQWJhiawsxPGq1TfA8SG&amp;usp=drive_fs</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1UWwbDG1UwOrhPRT6iPZwKNPTnXxa7d_6&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -650,9 +641,6 @@
     <t>https://drive.google.com/open?id=1RZNHMQd8ho6X3dWXtgAUDFym4XZtOPOe&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1Id0gnjn7IVYfpZ2RIoWM0WYzIsLHJy_7&amp;usp=drive_fs</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1UtZX4N8I-kDtlRE4p57ULKLQnHbzgqiA&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -1010,9 +998,6 @@
     <t>Przygrywka</t>
   </si>
   <si>
-    <t>Przygrywka, Rytm</t>
-  </si>
-  <si>
     <t>Akordy, Dwudźwięki</t>
   </si>
   <si>
@@ -1050,6 +1035,96 @@
   </si>
   <si>
     <t>https://youtu.be/jw8xYejrIUY?si=apLg-EEwbRPU29im</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyzwanie, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power chordy, Kostkowanie Naprzemienne, Palm Mute, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop D, Power chord, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwudźwięki, Kostkowanie w dół, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Granie palcami, Kostkowanie hybrydowe, </t>
+  </si>
+  <si>
+    <t>Galop, Legato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogrywanie akordów, CAGED, Slide, </t>
+  </si>
+  <si>
+    <t>D Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropped C </t>
+  </si>
+  <si>
+    <t>Szybki riff oparty o power chordy i kostkowanie naprzemienne z palm mute.</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło A</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło B</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1hHYCqi4v8OHqnd1TzLai13yg9xVnIvki&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1MpAiLDmoc0ulWrubjn9qYFiVVewr0zTa&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten riff miesza ze sobą pojedyncze dźwięki z uderzeniami akordów. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akordy, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riff zbudowany na szybkich, pojedynczych dźwiękach kostkowanych w dół, wraz z techniką slide. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Głównym elementem tego riffu jest tak zwany legato trill. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten riff przypomina trochę granie fingerstyle. W tym samym momencie musisz grać power chordy oraz wplecioną w tle melodię. Nie zapomnij przestroić gitary do Drop D. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legendarne intro zbudowane na dwóch dźwiękach w których da się zauważyć harmonię utworu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jest to intro transkrybowane z instrumentu klawiszowego na gitarę, przez co powstało nam ciekawe fingerstyle. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riff zbudowany na pojedynczych dźwiękach granych palcem serdecznym i wskazującym. Na koniec należy zagrać podciągnięcie z odpuszczeniem. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przygrywka, Rytm, Podciąganie strun, </t>
+  </si>
+  <si>
+    <t>Ten riff jest zbudowany w oparciu o ogrywanie akordów, ale tak naprawdę grasz dwa dźwięki w melodii, wokół których zmieniają się trzy basy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten riff to po prostu kilka power chordów, które musisz zagrać zgodnie z tabulaturą. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo szybki riff zbudowany w oparciu o tak zwany galop kostkowaniem naprzemiennym. Uwaga na zagrywkę na końcu, która pokonała niejednego gitarzystę. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To bardzo fajnie ułożone akordy w wyższych pozycjach, które należy ograć kostkowaniem. Akordy pochodzą z tak zwanego systemu Caged. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten riff łączy ze sobą bardzo trudne do złapania akordy, wraz z charakterystycznymi Hendrixowskimi zagrywkami na dwudźwiękach. </t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1215,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1154,6 +1229,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1702,7 +1781,7 @@
   <cols>
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="68.140625" customWidth="1"/>
@@ -1711,10 +1790,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>37</v>
@@ -1743,16 +1822,16 @@
         <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1766,16 +1845,16 @@
         <v>44</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1789,15 +1868,17 @@
         <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="G4" s="8"/>
+        <v>326</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -1810,17 +1891,17 @@
         <v>46</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
@@ -1831,325 +1912,377 @@
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="8"/>
+        <v>313</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="E14" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="8" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="8" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>205</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="8"/>
+        <v>316</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="C19" s="10" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="F19" s="4"/>
+        <v>315</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>363</v>
+      </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F20" s="4"/>
-      <c r="G20" s="8"/>
+      <c r="G20" s="8" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>43</v>
@@ -2158,171 +2291,177 @@
         <v>44</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="8" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F29" s="4"/>
-      <c r="G29" s="8"/>
+      <c r="G29" s="8" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F30" s="4"/>
-      <c r="G30" s="8"/>
+      <c r="G30" s="8" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F31" s="4"/>
-      <c r="G31" s="8"/>
+      <c r="G31" s="8" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>45</v>
@@ -2331,48 +2470,48 @@
         <v>46</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="8"/>
@@ -2382,94 +2521,94 @@
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="8" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="8"/>
@@ -2479,35 +2618,35 @@
         <v>27</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="8"/>
@@ -2517,73 +2656,73 @@
         <v>4</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="8"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="8"/>
@@ -2593,54 +2732,54 @@
         <v>2</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="8"/>
@@ -2650,35 +2789,37 @@
         <v>26</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F49" s="4"/>
-      <c r="G49" s="8"/>
+      <c r="G49" s="8" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="8"/>
@@ -2688,35 +2829,35 @@
         <v>22</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="8"/>
@@ -2726,16 +2867,16 @@
         <v>33</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="8"/>
@@ -2751,29 +2892,29 @@
         <v>44</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="8"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="8"/>
@@ -2783,23 +2924,23 @@
         <v>28</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>43</v>
@@ -2808,36 +2949,38 @@
         <v>44</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="8"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F58" s="4"/>
-      <c r="G58" s="8"/>
+      <c r="G58" s="8" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>45</v>
@@ -2846,10 +2989,10 @@
         <v>44</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="8"/>
@@ -2865,10 +3008,10 @@
         <v>44</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="8"/>
@@ -2878,16 +3021,16 @@
         <v>7</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="8"/>
@@ -2903,55 +3046,55 @@
         <v>44</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="8"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="8"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="8"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>45</v>
@@ -2960,86 +3103,86 @@
         <v>46</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="8"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="8"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="8"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="8"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="8"/>
@@ -3049,99 +3192,99 @@
         <v>29</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="8"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="8"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="8"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="8"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="8"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>43</v>
@@ -3150,10 +3293,10 @@
         <v>46</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="8"/>
@@ -3163,54 +3306,54 @@
         <v>30</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="8"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="8"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="8"/>
@@ -3220,339 +3363,339 @@
         <v>31</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="8"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="8"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="8"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="8"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="8"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="8"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="8"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="8"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="8"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="8"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="8"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="8"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="8"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="8"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="8"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="8"/>
@@ -3568,10 +3711,10 @@
         <v>46</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="8"/>
@@ -3581,16 +3724,16 @@
         <v>23</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="8"/>
@@ -3600,16 +3743,16 @@
         <v>19</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="8"/>
@@ -3625,17 +3768,17 @@
         <v>46</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="8"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>45</v>
@@ -3644,10 +3787,10 @@
         <v>46</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="8"/>
@@ -3657,16 +3800,16 @@
         <v>3</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="8"/>
@@ -3682,67 +3825,67 @@
         <v>46</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="8"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="8"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="8"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="8"/>
@@ -3752,16 +3895,16 @@
         <v>35</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="8"/>
@@ -3777,36 +3920,36 @@
         <v>46</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="8"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="8"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>45</v>
@@ -3815,10 +3958,10 @@
         <v>46</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="8"/>
@@ -3828,35 +3971,35 @@
         <v>5</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="8"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="8"/>
@@ -3866,137 +4009,137 @@
         <v>6</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="8"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="8"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="8"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="8"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="8"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="8"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F119" s="4"/>
       <c r="G119" s="8"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>45</v>
@@ -4005,74 +4148,74 @@
         <v>44</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="8"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F121" s="4"/>
       <c r="G121" s="8"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="8"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="8"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>45</v>
@@ -4081,14 +4224,14 @@
         <v>44</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="8" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -4102,10 +4245,10 @@
         <v>46</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F125" s="4"/>
       <c r="G125" s="8"/>
@@ -4121,10 +4264,10 @@
         <v>46</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="8"/>
@@ -4153,12 +4296,14 @@
     <hyperlink ref="C89" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
     <hyperlink ref="C96" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
     <hyperlink ref="C107" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
-    <hyperlink ref="C7" r:id="rId5" xr:uid="{BBF384E5-8C25-4A18-BE7D-85EEC8392C4E}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{BBF384E5-8C25-4A18-BE7D-85EEC8392C4E}"/>
     <hyperlink ref="C19" r:id="rId6" xr:uid="{91A4A065-747A-407A-B0CE-5F9B3BF29972}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{A1484470-F758-427A-8BC6-ADB24E480B76}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{422A23FB-E927-44A1-8543-D05FC652092F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT UTWORÓW - NPR.xlsx
+++ b/KONSPEKT UTWORÓW - NPR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C37E47D-8618-4466-A9B9-B8D1AED4B1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F366E28D-8A5B-4FB0-ADB2-608043323E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
@@ -1073,12 +1073,6 @@
     <t>Szybki riff oparty o power chordy i kostkowanie naprzemienne z palm mute.</t>
   </si>
   <si>
-    <t>Ale Wkoło Jest Wesoło A</t>
-  </si>
-  <si>
-    <t>Ale Wkoło Jest Wesoło B</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1hHYCqi4v8OHqnd1TzLai13yg9xVnIvki&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -1125,6 +1119,12 @@
   </si>
   <si>
     <t xml:space="preserve">Ten riff łączy ze sobą bardzo trudne do złapania akordy, wraz z charakterystycznymi Hendrixowskimi zagrywkami na dwudźwiękach. </t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło (A)</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło (B)</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>49</v>
@@ -1935,21 +1935,21 @@
         <v>332</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>314</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>49</v>
@@ -1958,13 +1958,13 @@
         <v>332</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>337</v>
@@ -1987,7 +1987,7 @@
         <v>313</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>336</v>
@@ -2010,7 +2010,7 @@
         <v>313</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>338</v>
@@ -2033,7 +2033,7 @@
         <v>314</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>339</v>
@@ -2056,7 +2056,7 @@
         <v>313</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>340</v>
@@ -2079,7 +2079,7 @@
         <v>313</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>340</v>
@@ -2102,10 +2102,10 @@
         <v>316</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -2125,7 +2125,7 @@
         <v>316</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>319</v>
@@ -2148,7 +2148,7 @@
         <v>314</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>318</v>
@@ -2171,7 +2171,7 @@
         <v>313</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>341</v>
@@ -2194,7 +2194,7 @@
         <v>313</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>342</v>
@@ -2217,7 +2217,7 @@
         <v>315</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G19" s="8"/>
     </row>

--- a/KONSPEKT UTWORÓW - NPR.xlsx
+++ b/KONSPEKT UTWORÓW - NPR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\HTML - NAJLEPSZE POLSKIE RIFFY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Documents\GitHub\najlepsze-polskie-riffy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F366E28D-8A5B-4FB0-ADB2-608043323E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A4BF3E-7260-47CE-9566-932FC8C058FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="370">
   <si>
     <t>Biała Armia</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Cykady na Cykladach</t>
   </si>
   <si>
-    <t>Kocham Cię Kochanie Moje</t>
-  </si>
-  <si>
     <t>Szerokie Wody</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>Dżentelmeni Metalu</t>
   </si>
   <si>
-    <t>Kiedy Powiem Sobie Dość</t>
-  </si>
-  <si>
     <t>Idź Precz</t>
   </si>
   <si>
@@ -425,9 +419,6 @@
     <t>Nie Rób Tyle Hałasu</t>
   </si>
   <si>
-    <t>Nie Wierz Nigdy Kobiecie</t>
-  </si>
-  <si>
     <t>Nie Wierze Skurwysynom</t>
   </si>
   <si>
@@ -740,15 +731,9 @@
     <t>https://drive.google.com/open?id=1Q3YDjLju6eIolxqu4pC78sygiNe80mCE&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1WeI20qcqZOpZ8Rs_1xAx3jOel0zFus61&amp;usp=drive_fs</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1Wh3pO4TudkMEYQbNVbz6Wcsr3cOUzZXw&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=11WCSb6eFDj9y_ncnph1A661E-XQOlFbm&amp;usp=drive_fs</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1kVLYxtinzKOjbVu3grZq5MhIzG8NU_x5&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -815,9 +800,6 @@
     <t>https://drive.google.com/open?id=1XzLQcWxwTvejIrh_EIzbn6AQj5Pj-bWO&amp;usp=drive_fs</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1Y1qnDr8VEL7NdVeWJr8xZUC8NMiEGLKX&amp;usp=drive_fs</t>
-  </si>
-  <si>
     <t>https://drive.google.com/open?id=1Y8FEumGobwIGDAmg6iAlq6CDnjwk16P5&amp;usp=drive_fs</t>
   </si>
   <si>
@@ -1121,10 +1103,46 @@
     <t xml:space="preserve">Ten riff łączy ze sobą bardzo trudne do złapania akordy, wraz z charakterystycznymi Hendrixowskimi zagrywkami na dwudźwiękach. </t>
   </si>
   <si>
-    <t>Ale Wkoło Jest Wesoło (A)</t>
-  </si>
-  <si>
-    <t>Ale Wkoło Jest Wesoło (B)</t>
+    <t>Kiedy  Powiem Sobie Dość [RIFF A]</t>
+  </si>
+  <si>
+    <t>Kiedy  Powiem Sobie Dość [RIFF B]</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ccoFD7pBav79wTMOSp90IJfPt6mylrTs&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1WpbZBQufVbwuAsHTqMtoeCTQy3k52ws8&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Kocham Cię Kochanie Moje [RIFF A]</t>
+  </si>
+  <si>
+    <t>Kocham Cię Kochanie Moje [RIFF B]</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=17KgN01ggjbpoJZXCvq9CJ0Bn702pUTWj&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=12vfZrots2a5LTsdPhLIEy3P2pFdubfyW&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>Nie wierz nigdy kobiecie [RIFF A]</t>
+  </si>
+  <si>
+    <t>Nie wierz nigdy kobiecie [RIFF B]</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło [RIFF A]</t>
+  </si>
+  <si>
+    <t>Ale Wkoło Jest Wesoło [RIFF B]</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1sKBxm895nh5IXUMIi0X5fuq8WUQYWZSm&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=11kwrZ0SeedmPFjIAR_jEHO1sDAN7Ff5G&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1233,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1233,6 +1251,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -1435,10 +1454,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}" name="Tabela1" displayName="Tabela1" ref="A1:G128" tableType="xml" totalsRowShown="0" tableBorderDxfId="7" connectionId="1">
-  <autoFilter ref="A1:G128" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G128">
-    <sortCondition ref="A1:A128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}" name="Tabela1" displayName="Tabela1" ref="A1:G131" tableType="xml" totalsRowShown="0" tableBorderDxfId="7" connectionId="1">
+  <autoFilter ref="A1:G131" xr:uid="{04A0E095-C462-473D-830F-EBC727B64385}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G131">
+    <sortCondition ref="A1:A131"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{6FF1AA77-FAFD-461A-9D1E-E1F2F29A966E}" uniqueName="tytul" name="UTWÓR" dataDxfId="6">
@@ -1776,13 +1795,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="68.140625" customWidth="1"/>
     <col min="7" max="7" width="29.85546875" customWidth="1"/>
@@ -1790,71 +1809,71 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1862,42 +1881,42 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G5" s="8"/>
     </row>
@@ -1906,137 +1925,137 @@
         <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -2044,91 +2063,91 @@
         <v>0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2136,110 +2155,110 @@
         <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="8" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2247,271 +2266,271 @@
         <v>21</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="8" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="8" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="8" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="8" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="8"/>
@@ -2521,132 +2540,132 @@
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="8" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="8"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="8"/>
@@ -2656,73 +2675,73 @@
         <v>4</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="8"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="8"/>
@@ -2732,1570 +2751,1629 @@
         <v>2</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="8"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>26</v>
+      <c r="A49" s="13" t="s">
+        <v>356</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>235</v>
+        <v>358</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="8" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>104</v>
+        <v>357</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>236</v>
+        <v>359</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F50" s="4"/>
-      <c r="G50" s="8"/>
+      <c r="G50" s="8" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>106</v>
+      <c r="A52" s="13" t="s">
+        <v>360</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>238</v>
+        <v>362</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="8"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>33</v>
+        <v>361</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>239</v>
+        <v>363</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>240</v>
+      <c r="D54" s="6" t="s">
+        <v>233</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="8"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="8"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>242</v>
+        <v>42</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>235</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="8"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F58" s="4"/>
-      <c r="G58" s="8" t="s">
-        <v>344</v>
-      </c>
+      <c r="G58" s="8"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="8"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F60" s="4"/>
-      <c r="G60" s="8"/>
+      <c r="G60" s="8" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>248</v>
+        <v>42</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="8"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="8"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>250</v>
+        <v>42</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="8"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>251</v>
+        <v>42</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="8"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="8"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>253</v>
+      <c r="D67" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="8"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="8"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="8"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="8"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="8"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="8"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="8"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="8"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="8"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
-        <v>30</v>
+      <c r="A76" s="13" t="s">
+        <v>364</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="8"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>132</v>
+        <v>365</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>263</v>
+        <v>369</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="8"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="8"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="8"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="8"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="8"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="8"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="8"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="8"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="8"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="8"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="8"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>329</v>
+        <v>142</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="8"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="8"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="8"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>44</v>
+        <v>147</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="8"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="8"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="8"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>330</v>
+        <v>76</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="8"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="8"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>324</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="8"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="8"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="8"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>288</v>
+        <v>42</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="8"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="8"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="8"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>164</v>
+        <v>3</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D105" s="6" t="s">
-        <v>291</v>
+      <c r="D105" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="8"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>165</v>
+        <v>15</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="8"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>331</v>
+        <v>138</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="8"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="8"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="8"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="8"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="8"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="8"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>6</v>
+        <v>166</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="8"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>172</v>
+        <v>5</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="8"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="8"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="8"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>328</v>
+        <v>170</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="8"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="8"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F119" s="4"/>
       <c r="G119" s="8"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>44</v>
+        <v>175</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="8"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F121" s="4"/>
       <c r="G121" s="8"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="8"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="8"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D124" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="F124" s="4"/>
-      <c r="G124" s="8" t="s">
-        <v>321</v>
-      </c>
+      <c r="G124" s="8"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F125" s="4"/>
       <c r="G125" s="8"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="8"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="1"/>
+      <c r="A127" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>311</v>
+      </c>
       <c r="F127" s="4"/>
-      <c r="G127" s="8"/>
+      <c r="G127" s="8" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="1"/>
+      <c r="A128" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>308</v>
+      </c>
       <c r="F128" s="4"/>
       <c r="G128" s="8"/>
     </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F129" s="4"/>
+      <c r="G129" s="8"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="8"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C117" r:id="rId1" xr:uid="{E336D330-01D4-458D-BDE6-2A361C74F038}"/>
-    <hyperlink ref="C89" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
-    <hyperlink ref="C96" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
-    <hyperlink ref="C107" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
+    <hyperlink ref="C120" r:id="rId1" xr:uid="{E336D330-01D4-458D-BDE6-2A361C74F038}"/>
+    <hyperlink ref="C92" r:id="rId2" xr:uid="{51B394D9-4BD9-4364-A784-5ACD4BF14198}"/>
+    <hyperlink ref="C99" r:id="rId3" xr:uid="{3C0F71B7-6DBC-4577-94F2-B848674E7F04}"/>
+    <hyperlink ref="C110" r:id="rId4" xr:uid="{926771A3-978D-48BB-837E-0D7E12C88831}"/>
     <hyperlink ref="C8" r:id="rId5" xr:uid="{BBF384E5-8C25-4A18-BE7D-85EEC8392C4E}"/>
     <hyperlink ref="C19" r:id="rId6" xr:uid="{91A4A065-747A-407A-B0CE-5F9B3BF29972}"/>
     <hyperlink ref="C7" r:id="rId7" xr:uid="{A1484470-F758-427A-8BC6-ADB24E480B76}"/>

--- a/KONSPEKT UTWORÓW - NPR.xlsx
+++ b/KONSPEKT UTWORÓW - NPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Documents\GitHub\najlepsze-polskie-riffy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A4BF3E-7260-47CE-9566-932FC8C058FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B717EE4-5E28-42A3-83AE-A9C03EF1200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{081E8F71-F0AA-48DE-8939-338A57B7A302}"/>
   </bookViews>
